--- a/research/traditional_assets/database/data/estonia/estonia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_financial_svcs_non_bank_insurance.xlsx
@@ -594,16 +594,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.8986175115207373</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="J2">
-        <v>0.8986175115207373</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="K2">
-        <v>0.165</v>
+        <v>0.429</v>
       </c>
       <c r="L2">
-        <v>0.7603686635944701</v>
+        <v>1.021428571428571</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,64 +630,64 @@
         <v>0.001</v>
       </c>
       <c r="V2">
-        <v>0.0003311258278145695</v>
+        <v>0.0005586592178770949</v>
       </c>
       <c r="W2">
-        <v>0.0237410071942446</v>
+        <v>0.06172661870503597</v>
       </c>
       <c r="X2">
-        <v>0.03500458504015159</v>
+        <v>0.05133373670575946</v>
       </c>
       <c r="Y2">
-        <v>-0.01126357784590698</v>
+        <v>0.01039288199927652</v>
       </c>
       <c r="Z2">
-        <v>0.01671931581785962</v>
+        <v>0.0370403033777229</v>
       </c>
       <c r="AA2">
-        <v>0.01502426997457431</v>
+        <v>0.03439456742217126</v>
       </c>
       <c r="AB2">
-        <v>0.06111764967545651</v>
+        <v>0.054898810071369</v>
       </c>
       <c r="AC2">
-        <v>-0.0460933797008822</v>
+        <v>-0.02050424264919774</v>
       </c>
       <c r="AD2">
-        <v>4.39</v>
+        <v>0.254</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>4.39</v>
+        <v>0.254</v>
       </c>
       <c r="AG2">
-        <v>4.388999999999999</v>
+        <v>0.253</v>
       </c>
       <c r="AH2">
-        <v>0.592442645074224</v>
+        <v>0.12426614481409</v>
       </c>
       <c r="AI2">
-        <v>0.3871252204585537</v>
+        <v>0.04114026563006155</v>
       </c>
       <c r="AJ2">
-        <v>0.5923876366581186</v>
+        <v>0.1238374938815467</v>
       </c>
       <c r="AK2">
-        <v>0.3870711702972043</v>
+        <v>0.04098493439170581</v>
       </c>
       <c r="AL2">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="AM2">
-        <v>0.036</v>
+        <v>-0.03800000000000001</v>
       </c>
       <c r="AO2">
-        <v>5.416666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="AQ2">
-        <v>5.416666666666667</v>
+        <v>-10.26315789473684</v>
       </c>
     </row>
     <row r="3">
@@ -713,16 +713,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8986175115207373</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="J3">
-        <v>0.8986175115207373</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="K3">
-        <v>0.165</v>
+        <v>0.429</v>
       </c>
       <c r="L3">
-        <v>0.7603686635944701</v>
+        <v>1.021428571428571</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,64 +749,64 @@
         <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0.0003311258278145695</v>
+        <v>0.0005586592178770949</v>
       </c>
       <c r="W3">
-        <v>0.0237410071942446</v>
+        <v>0.06172661870503597</v>
       </c>
       <c r="X3">
-        <v>0.03500458504015159</v>
+        <v>0.05133373670575946</v>
       </c>
       <c r="Y3">
-        <v>-0.01126357784590698</v>
+        <v>0.01039288199927652</v>
       </c>
       <c r="Z3">
-        <v>0.01671931581785962</v>
+        <v>0.0370403033777229</v>
       </c>
       <c r="AA3">
-        <v>0.01502426997457431</v>
+        <v>0.03439456742217126</v>
       </c>
       <c r="AB3">
-        <v>0.06111764967545651</v>
+        <v>0.054898810071369</v>
       </c>
       <c r="AC3">
-        <v>-0.0460933797008822</v>
+        <v>-0.02050424264919774</v>
       </c>
       <c r="AD3">
-        <v>4.39</v>
+        <v>0.254</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4.39</v>
+        <v>0.254</v>
       </c>
       <c r="AG3">
-        <v>4.388999999999999</v>
+        <v>0.253</v>
       </c>
       <c r="AH3">
-        <v>0.592442645074224</v>
+        <v>0.12426614481409</v>
       </c>
       <c r="AI3">
-        <v>0.3871252204585537</v>
+        <v>0.04114026563006155</v>
       </c>
       <c r="AJ3">
-        <v>0.5923876366581186</v>
+        <v>0.1238374938815467</v>
       </c>
       <c r="AK3">
-        <v>0.3870711702972043</v>
+        <v>0.04098493439170581</v>
       </c>
       <c r="AL3">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="AM3">
-        <v>0.036</v>
+        <v>-0.03800000000000001</v>
       </c>
       <c r="AO3">
-        <v>5.416666666666667</v>
+        <v>3.25</v>
       </c>
       <c r="AQ3">
-        <v>5.416666666666667</v>
+        <v>-10.26315789473684</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/estonia/estonia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -594,16 +594,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.9285714285714286</v>
+        <v>0.9243876464323748</v>
       </c>
       <c r="J2">
-        <v>0.9285714285714286</v>
+        <v>0.9243876464323748</v>
       </c>
       <c r="K2">
-        <v>0.429</v>
+        <v>0.863</v>
       </c>
       <c r="L2">
-        <v>1.021428571428571</v>
+        <v>0.9190628328008519</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,67 +627,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.001</v>
+        <v>0.007</v>
       </c>
       <c r="V2">
-        <v>0.0005586592178770949</v>
+        <v>6.692160611854685e-05</v>
       </c>
       <c r="W2">
-        <v>0.06172661870503597</v>
+        <v>0.06894707207207207</v>
       </c>
       <c r="X2">
-        <v>0.05133373670575946</v>
+        <v>0.05228727464604656</v>
       </c>
       <c r="Y2">
-        <v>0.01039288199927652</v>
+        <v>0.01665979742602551</v>
       </c>
       <c r="Z2">
-        <v>0.0370403033777229</v>
+        <v>0.07319354587263231</v>
       </c>
       <c r="AA2">
-        <v>0.03439456742217126</v>
+        <v>0.06783753730576082</v>
       </c>
       <c r="AB2">
-        <v>0.054898810071369</v>
+        <v>0.05228727464604656</v>
       </c>
       <c r="AC2">
-        <v>-0.02050424264919774</v>
+        <v>0.01555026265971426</v>
       </c>
       <c r="AD2">
-        <v>0.254</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.254</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.253</v>
+        <v>-0.007</v>
       </c>
       <c r="AH2">
-        <v>0.12426614481409</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.04114026563006155</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.1238374938815467</v>
+        <v>-6.69260849196409e-05</v>
       </c>
       <c r="AK2">
-        <v>0.04098493439170581</v>
+        <v>-0.0004725578883413218</v>
       </c>
       <c r="AL2">
-        <v>0.12</v>
+        <v>0.007</v>
       </c>
       <c r="AM2">
-        <v>-0.03800000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="AO2">
-        <v>3.25</v>
+        <v>124</v>
       </c>
       <c r="AQ2">
-        <v>-10.26315789473684</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
@@ -713,16 +713,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9285714285714286</v>
+        <v>0.9511677282377921</v>
       </c>
       <c r="J3">
-        <v>0.9285714285714286</v>
+        <v>0.9511677282377921</v>
       </c>
       <c r="K3">
-        <v>0.429</v>
+        <v>0.443</v>
       </c>
       <c r="L3">
-        <v>1.021428571428571</v>
+        <v>0.940552016985138</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -746,67 +746,180 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="V3">
-        <v>0.0005586592178770949</v>
+        <v>2.949852507374631e-05</v>
       </c>
       <c r="W3">
-        <v>0.06172661870503597</v>
+        <v>0.07483108108108108</v>
       </c>
       <c r="X3">
-        <v>0.05133373670575946</v>
+        <v>0.05228727464604656</v>
       </c>
       <c r="Y3">
-        <v>0.01039288199927652</v>
+        <v>0.02254380643503452</v>
       </c>
       <c r="Z3">
-        <v>0.0370403033777229</v>
+        <v>0.07630001619957882</v>
       </c>
       <c r="AA3">
-        <v>0.03439456742217126</v>
+        <v>0.07257411307306011</v>
       </c>
       <c r="AB3">
-        <v>0.054898810071369</v>
+        <v>0.05228727464604656</v>
       </c>
       <c r="AC3">
-        <v>-0.02050424264919774</v>
+        <v>0.02028683842701355</v>
       </c>
       <c r="AD3">
-        <v>0.254</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.254</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.253</v>
+        <v>-0.002</v>
       </c>
       <c r="AH3">
-        <v>0.12426614481409</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.04114026563006155</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.1238374938815467</v>
+        <v>-2.949939526239712e-05</v>
       </c>
       <c r="AK3">
-        <v>0.04098493439170581</v>
+        <v>-0.0002805836139169473</v>
       </c>
       <c r="AL3">
-        <v>0.12</v>
+        <v>0.007</v>
       </c>
       <c r="AM3">
-        <v>-0.03800000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="AO3">
-        <v>3.25</v>
+        <v>64</v>
       </c>
       <c r="AQ3">
-        <v>-10.26315789473684</v>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Atlantis SE (WSE:ATS)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.8974358974358974</v>
+      </c>
+      <c r="J4">
+        <v>0.8974358974358974</v>
+      </c>
+      <c r="K4">
+        <v>0.42</v>
+      </c>
+      <c r="L4">
+        <v>0.8974358974358974</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.005</v>
+      </c>
+      <c r="V4">
+        <v>0.0001358695652173913</v>
+      </c>
+      <c r="W4">
+        <v>0.06306306306306306</v>
+      </c>
+      <c r="X4">
+        <v>0.05228727464604656</v>
+      </c>
+      <c r="Y4">
+        <v>0.0107757884170165</v>
+      </c>
+      <c r="Z4">
+        <v>0.0703125</v>
+      </c>
+      <c r="AA4">
+        <v>0.06310096153846154</v>
+      </c>
+      <c r="AB4">
+        <v>0.05228727464604656</v>
+      </c>
+      <c r="AC4">
+        <v>0.01081368689241498</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-0.005</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.0001358880282647099</v>
+      </c>
+      <c r="AK4">
+        <v>-0.0006506180871828236</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
